--- a/example_data/production/pv-input.xlsx
+++ b/example_data/production/pv-input.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t xml:space="preserve">block_identifier</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">emission_cost</t>
   </si>
   <si>
+    <t xml:space="preserve">representative_unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Explanation of the data columns in Sheet1:</t>
   </si>
   <si>
@@ -74,7 +77,7 @@
     <t xml:space="preserve">name of the unit. Does not have to be unique for different blocks.</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternative which the given values are for</t>
+    <t xml:space="preserve">Alternative which the given values are for. Usually “Base”.</t>
   </si>
   <si>
     <t xml:space="preserve">Capacity of the unit. Usually given as time series. In that case the correct value is ts:timeseriesname, where a time series CSV file with timeseriesname must be found in the input folder. </t>
@@ -105,6 +108,9 @@
   </si>
   <si>
     <t xml:space="preserve">€/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“X” indicates that the unit capacity data will be used when selecting representative periods.</t>
   </si>
 </sst>
 </file>
@@ -199,7 +205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -214,6 +220,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -423,7 +433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.93"/>
@@ -435,6 +445,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -468,126 +479,153 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
+      <c r="K15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
+      <c r="K21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
+      <c r="K22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
+      <c r="K23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
+      <c r="K24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
@@ -707,14 +745,20 @@
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="4"/>
+      <c r="D54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="5"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K25" type="list">
+      <formula1>"X"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -730,7 +774,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:C14"/>
+  <dimension ref="A2:C15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.24"/>
@@ -738,118 +782,127 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="28.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" customFormat="false" ht="46.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="34.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="28.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="46.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="34.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="B15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
